--- a/sources/metaPee/combined/provisional_ui/subexposure_views/no/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_combined.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/no/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_combined.xlsx
@@ -1093,86 +1093,90 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.7716686738745262</v>
+        <v>0.76958797865763</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.6812676670885198</v>
+        <v>0.6985838950869678</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.8741528788765721</v>
+        <v>0.8478089189568343</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.630272139746614</v>
+        <v>0.5102524008301633</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9447863941418472</v>
+        <v>1.160730759778378</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>881922</v>
+        <v>14155769</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4765</v>
+        <v>29965</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>betaine</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.78</v>
+        <v>0.7716686738745262</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.49</v>
+        <v>0.6812676670885198</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+        <v>0.8741528788765721</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.630272139746614</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.9447863941418472</v>
+      </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
-        <v>77208</v>
+        <v>881922</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>225</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zeaxanthin</t>
+          <t>betaine</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.7908871412226887</v>
+        <v>0.78</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.672266795591652</v>
+        <v>0.49</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.9305308958112057</v>
+        <v>1.24</v>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1181,29 +1185,29 @@
       </c>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>781129</v>
+        <v>77208</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2616</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vitamin_b3</t>
+          <t>zeaxanthin</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.8008327058475403</v>
+        <v>0.7908871412226887</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.6012503602491741</v>
+        <v>0.672266795591652</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.069610736564642</v>
+        <v>0.9305308958112057</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1212,45 +1216,41 @@
       </c>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>2301</v>
+        <v>781129</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>767</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>vitamin_b3</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.8016365126306161</v>
+        <v>0.8008327058475403</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.7357977457414276</v>
+        <v>0.6012503602491741</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.8734538362278126</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.5503404917681979</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>1.167679115010942</v>
-      </c>
+        <v>1.069610736564642</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>14535196</v>
+        <v>2301</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>30994</v>
+        <v>767</v>
       </c>
     </row>
     <row r="25">
@@ -1520,20 +1520,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1.099713607906872</v>
+        <v>1.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.8702945807931509</v>
+        <v>0.92</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.388589318228265</v>
+        <v>1.32</v>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
@@ -1542,16 +1542,16 @@
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>120852</v>
+        <v>774952</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>485</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>monounsaturated_fat_mufa</t>
+          <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1561,10 +1561,10 @@
         <v>1.1</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
@@ -1582,121 +1582,121 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>polyunsaturated_fat_pufa</t>
+          <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>1.105391974364155</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9570496576537233</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+        <v>1.276599624884141</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.2118725844161015</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>5.767104886911577</v>
+      </c>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>774952</v>
+        <v>563999</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1478</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sugar_sweetened_beverage_intake</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.105391974364155</v>
+        <v>1.149239018159417</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.9570496576537233</v>
+        <v>0.9369737613162469</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.276599624884141</v>
+        <v>1.409591575973965</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.2118725844161015</v>
+        <v>0.6296319129363084</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5.767104886911577</v>
+        <v>2.09765466731294</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>563999</v>
+        <v>1766660</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1503</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>ultra_processed_food_intake</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.149239018159417</v>
+        <v>1.159516828778204</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.9369737613162469</v>
+        <v>1.049863300995226</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1.409591575973965</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
+        <v>1.289026327823149</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>1766660</v>
+        <v>480347</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5212</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ultra_processed_food_intake</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1.159516828778204</v>
+        <v>1.225562595253664</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.049863300995226</v>
+        <v>0.5280311504245172</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1.289026327823149</v>
+        <v>2.844820578397655</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr"/>
@@ -1705,29 +1705,29 @@
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>480347</v>
+        <v>4597</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3330</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>manganese</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1.225562595253664</v>
+        <v>1.259147309219077</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.5280311504245172</v>
+        <v>0.8303675352604869</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2.844820578397655</v>
+        <v>1.905481103347211</v>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr"/>
@@ -1736,29 +1736,29 @@
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
-        <v>4597</v>
+        <v>61321</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1909</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>manganese</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.259147309219077</v>
+        <v>1.279067174104721</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.8303675352604869</v>
+        <v>0.8702945807931509</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.905481103347211</v>
+        <v>1.895554083552581</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>61321</v>
+        <v>120852</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>229</v>
+        <v>485</v>
       </c>
     </row>
     <row r="41">
@@ -2063,20 +2063,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2.441469226259395</v>
+        <v>2.29437373176878</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.4308048825855873</v>
+        <v>1.357459324829277</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>13.83774495311215</v>
+        <v>3.871032294091838</v>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
@@ -2085,29 +2085,29 @@
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="2" t="n">
-        <v>95958</v>
+        <v>534</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>353</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2.588334629698914</v>
+        <v>2.441469226259395</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1.525795715679317</v>
+        <v>0.4308048825855873</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>4.390787859890018</v>
+        <v>13.83774495311215</v>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>534</v>
+        <v>95958</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>267</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
